--- a/data/employees/EMP097/AST-EMP097-06.xlsx
+++ b/data/employees/EMP097/AST-EMP097-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment Inventory Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,166 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Equipment Inventory Tracker - Riley Patel (Manufacturing)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Riley Patel | Role: Architect | Location: Bengaluru | Date: 2025-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp097 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>93</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp097 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>85</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Line ID</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>OEE %</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Downtime (min)</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Units Produced</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Defect Rate %</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp097 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>86</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L-01</t>
+          <t>EMP097</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CNC Mill A</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="D5" t="n">
-        <v>12</v>
+          <t>Ast Emp097 06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>4200</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.8</v>
+        <v>95</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L-02</t>
+          <t>EMP097</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Assembly Arm B</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>91</v>
-      </c>
-      <c r="D6" t="n">
-        <v>5</v>
+          <t>Ast Emp097 06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>5100</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.3</v>
+        <v>79</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L-03</t>
+          <t>EMP097</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Conveyor Unit C</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="D7" t="n">
-        <v>45</v>
+          <t>Ast Emp097 06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>3800</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.2</v>
+        <v>80</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L-04</t>
+          <t>EMP097</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Laser Cutter D</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3</v>
+          <t>Ast Emp097 06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.1</v>
+        <v>72</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp097 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>73</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp097 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>74</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp097 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>97</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp097 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>89</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp097 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>71</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp097 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>82</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp097 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>73</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp097 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>77</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp097 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>83</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp097 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>66</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp097 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>62</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp097 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>72</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp097 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>90</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp097 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>93</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp097 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>70</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp097 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>96</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp097 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>95</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP097</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP097 contributes to ast emp097 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>